--- a/docs/IMPROVEMENT_TODO.xlsx
+++ b/docs/IMPROVEMENT_TODO.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -948,7 +948,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>

--- a/docs/IMPROVEMENT_TODO.xlsx
+++ b/docs/IMPROVEMENT_TODO.xlsx
@@ -2950,10 +2950,14 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>/blog/c04-josler-sougou-kousatsu-kakikata</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3068,10 +3072,14 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
+          <t>公開済</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>/blog/b02-josler-160cases</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
